--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -429,7 +429,7 @@
         <v>Tender</v>
       </c>
       <c r="B3" t="str">
-        <v>Wave 2 governed CCTV Tender r1daco4</v>
+        <v>Wave 2 governed CCTV Tender r1mgoli</v>
       </c>
     </row>
     <row r="4">
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>a94bf63d-75ae-4ce1-af80-d9d88fad9e00</v>
+        <v>064942ff-eb92-4350-9034-7f23f51c8fd9</v>
       </c>
     </row>
     <row r="5">
@@ -445,7 +445,7 @@
         <v>Tender reference</v>
       </c>
       <c r="B5" t="str">
-        <v>W2-TDR-1789397954165</v>
+        <v>W2-TDR-1789413291024</v>
       </c>
     </row>
     <row r="6">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>a4785a45-4c8d-4b08-8a0d-14786ae4a2b6</v>
+        <v>8ad9559a-fb6e-4236-bcfe-a37885bc3427</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>a8ea68e5-3514-409f-b1df-66581dfa9f38</v>
+        <v>c51ca5c2-4fdd-4948-a23d-67e8b4cac0fa</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>26d28f1b-e127-46b8-8933-2d51f9e6c489</v>
+        <v>f3115777-7554-4a4e-b174-ac22980bbb21</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-14T14:59:15.702Z</v>
+        <v>2026-09-14T19:14:51.601Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>fafd0651-cb92-479a-af86-9b8f1d53df20</v>
+        <v>da0b6faf-c847-48ee-a8fa-9f2f5af7b340</v>
       </c>
       <c r="B2" t="str">
-        <v>468c6d19-238e-44a1-95ff-8b689cda78db</v>
+        <v>ddbb5116-4724-409c-8513-ac4aa3195f4c</v>
       </c>
       <c r="C2" t="str">
-        <v>a4785a45-4c8d-4b08-8a0d-14786ae4a2b6</v>
+        <v>8ad9559a-fb6e-4236-bcfe-a37885bc3427</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -421,7 +421,7 @@
         <v>Company</v>
       </c>
       <c r="B2" t="str">
-        <v>AURA MEP Systems Test L.L.C.</v>
+        <v>J1 Audit MEP L.L.C.</v>
       </c>
     </row>
     <row r="3">
@@ -429,7 +429,7 @@
         <v>Tender</v>
       </c>
       <c r="B3" t="str">
-        <v>Wave 2 governed CCTV Tender r1mgoli</v>
+        <v>J1 fictional MEP tender</v>
       </c>
     </row>
     <row r="4">
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>064942ff-eb92-4350-9034-7f23f51c8fd9</v>
+        <v>5e82c4f6-8874-4df7-a260-a46645ab09c8</v>
       </c>
     </row>
     <row r="5">
@@ -445,7 +445,7 @@
         <v>Tender reference</v>
       </c>
       <c r="B5" t="str">
-        <v>W2-TDR-1789413291024</v>
+        <v>TND-2026-000001</v>
       </c>
     </row>
     <row r="6">
@@ -453,7 +453,7 @@
         <v>Client</v>
       </c>
       <c r="B6" t="str">
-        <v>Wave 2 fictional client</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>Approved Technical Study</v>
       </c>
       <c r="B9" t="str">
-        <v>CCTV technical proposal basis</v>
+        <v>J1 structured MEP tender study</v>
       </c>
     </row>
     <row r="10">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>8ad9559a-fb6e-4236-bcfe-a37885bc3427</v>
+        <v>c290d755-7cdc-434e-b522-69ea25920fb8</v>
       </c>
     </row>
     <row r="11">
@@ -501,7 +501,7 @@
         <v>Client input revision</v>
       </c>
       <c r="B12" t="str">
-        <v>Client specification Rev 03</v>
+        <v>Tender addendum Rev 03</v>
       </c>
     </row>
     <row r="13">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>c51ca5c2-4fdd-4948-a23d-67e8b4cac0fa</v>
+        <v>9aec6c6f-eddb-46ba-b2b7-b49a58a5713a</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>f3115777-7554-4a4e-b174-ac22980bbb21</v>
+        <v>68ced2e8-806a-49ab-836a-ff81d084fac0</v>
       </c>
     </row>
     <row r="15">
@@ -525,7 +525,7 @@
         <v>Quantity source revision</v>
       </c>
       <c r="B15" t="str">
-        <v>technical-study:S-001:Client specification Rev 03</v>
+        <v>technical-study:S-001:Tender addendum Rev 03</v>
       </c>
     </row>
     <row r="16">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-14T19:14:51.601Z</v>
+        <v>2026-09-17T13:46:21.773Z</v>
       </c>
     </row>
     <row r="17">
@@ -541,7 +541,7 @@
         <v>Quantity projected by</v>
       </c>
       <c r="B17" t="str">
-        <v>u-admin</v>
+        <v>j1-estimator</v>
       </c>
     </row>
     <row r="18">
@@ -565,7 +565,7 @@
         <v>Total direct cost</v>
       </c>
       <c r="B20">
-        <v>2400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="21">
@@ -605,7 +605,7 @@
         <v>Total selling value</v>
       </c>
       <c r="B25">
-        <v>2400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="26">
@@ -621,7 +621,7 @@
         <v>Estimated Tender value</v>
       </c>
       <c r="B27">
-        <v>2400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="28">
@@ -829,31 +829,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>da0b6faf-c847-48ee-a8fa-9f2f5af7b340</v>
+        <v>f95548da-494f-4c82-a639-297f30b14a70</v>
       </c>
       <c r="B2" t="str">
-        <v>ddbb5116-4724-409c-8513-ac4aa3195f4c</v>
+        <v>4d92f53c-a11d-4265-a925-c8b800cfabb2</v>
       </c>
       <c r="C2" t="str">
-        <v>8ad9559a-fb6e-4236-bcfe-a37885bc3427</v>
+        <v>c290d755-7cdc-434e-b522-69ea25920fb8</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>Client specification Rev 03</v>
+        <v>Tender addendum Rev 03</v>
       </c>
       <c r="F2" t="str">
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>IP camera complete</v>
+        <v>Fictional MEP control point</v>
       </c>
       <c r="H2" t="str">
         <v>no</v>
       </c>
       <c r="I2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -922,7 +922,7 @@
         <v/>
       </c>
       <c r="AF2">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -949,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AP2">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="AQ2">
         <v>0</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>5e82c4f6-8874-4df7-a260-a46645ab09c8</v>
+        <v>990e3a71-8c7b-4c5a-8a25-bc105bdb6967</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>c290d755-7cdc-434e-b522-69ea25920fb8</v>
+        <v>4de05602-2211-45ca-91d6-21abc29cac12</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>9aec6c6f-eddb-46ba-b2b7-b49a58a5713a</v>
+        <v>17fa70cc-10c9-4f47-917a-1878b9d2a65d</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>68ced2e8-806a-49ab-836a-ff81d084fac0</v>
+        <v>c67b78f2-b569-4f0a-ae9b-e8b3d7601fc3</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-17T13:46:21.773Z</v>
+        <v>2026-09-18T04:44:26.035Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>f95548da-494f-4c82-a639-297f30b14a70</v>
+        <v>4660a24a-419e-465b-b54b-9511a8a62518</v>
       </c>
       <c r="B2" t="str">
-        <v>4d92f53c-a11d-4265-a925-c8b800cfabb2</v>
+        <v>8cbe41a2-fe66-4880-aa25-9646a77c384c</v>
       </c>
       <c r="C2" t="str">
-        <v>c290d755-7cdc-434e-b522-69ea25920fb8</v>
+        <v>4de05602-2211-45ca-91d6-21abc29cac12</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>990e3a71-8c7b-4c5a-8a25-bc105bdb6967</v>
+        <v>d861ff69-84d3-4d9d-928f-df926021d3ef</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>4de05602-2211-45ca-91d6-21abc29cac12</v>
+        <v>0fe64ffe-c657-40f8-ac0b-ad4880ead2e0</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>17fa70cc-10c9-4f47-917a-1878b9d2a65d</v>
+        <v>2d497abc-14e6-47d2-9349-04fc02ddc681</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>c67b78f2-b569-4f0a-ae9b-e8b3d7601fc3</v>
+        <v>cff1eac4-58a5-42f8-b128-6627c61488d0</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-18T04:44:26.035Z</v>
+        <v>2026-09-18T05:16:52.895Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>4660a24a-419e-465b-b54b-9511a8a62518</v>
+        <v>fc853ad9-7541-41a9-bc8c-97644f88c57a</v>
       </c>
       <c r="B2" t="str">
-        <v>8cbe41a2-fe66-4880-aa25-9646a77c384c</v>
+        <v>bb34a1d2-b55b-457f-b986-d81896f5fc41</v>
       </c>
       <c r="C2" t="str">
-        <v>4de05602-2211-45ca-91d6-21abc29cac12</v>
+        <v>0fe64ffe-c657-40f8-ac0b-ad4880ead2e0</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>d861ff69-84d3-4d9d-928f-df926021d3ef</v>
+        <v>6804bc65-7d9c-421a-be03-234264f2f8bd</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>0fe64ffe-c657-40f8-ac0b-ad4880ead2e0</v>
+        <v>edd694bb-4eb0-45b1-9812-b69dd415bb1e</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>2d497abc-14e6-47d2-9349-04fc02ddc681</v>
+        <v>90e66c55-7f62-46ef-a950-c8d4d6976b4a</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>cff1eac4-58a5-42f8-b128-6627c61488d0</v>
+        <v>afa8401f-778b-4cb4-80e5-b39f793b3872</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-18T05:16:52.895Z</v>
+        <v>2026-09-18T05:57:20.498Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>fc853ad9-7541-41a9-bc8c-97644f88c57a</v>
+        <v>160b7ae5-87e6-46b5-98f1-90fa1298d646</v>
       </c>
       <c r="B2" t="str">
-        <v>bb34a1d2-b55b-457f-b986-d81896f5fc41</v>
+        <v>ce2dbc85-ccdb-47ef-a2b5-c0040465630f</v>
       </c>
       <c r="C2" t="str">
-        <v>0fe64ffe-c657-40f8-ac0b-ad4880ead2e0</v>
+        <v>edd694bb-4eb0-45b1-9812-b69dd415bb1e</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>6804bc65-7d9c-421a-be03-234264f2f8bd</v>
+        <v>f8b3b07e-b381-4bc5-a8ad-382ad189a9eb</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>edd694bb-4eb0-45b1-9812-b69dd415bb1e</v>
+        <v>a99bff34-c1b8-4ff2-a9ab-7b29d74471b0</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>90e66c55-7f62-46ef-a950-c8d4d6976b4a</v>
+        <v>cd81d97b-0b7e-40e2-b4aa-16dd09663cd5</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>afa8401f-778b-4cb4-80e5-b39f793b3872</v>
+        <v>2274ef39-35af-4e6b-bf6c-61528af791a3</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-18T05:57:20.498Z</v>
+        <v>2026-09-18T07:58:34.037Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>160b7ae5-87e6-46b5-98f1-90fa1298d646</v>
+        <v>2ee01bda-f81e-4382-acb7-233ff975f857</v>
       </c>
       <c r="B2" t="str">
-        <v>ce2dbc85-ccdb-47ef-a2b5-c0040465630f</v>
+        <v>390c4952-6e15-4b47-b902-1b7a21d792de</v>
       </c>
       <c r="C2" t="str">
-        <v>edd694bb-4eb0-45b1-9812-b69dd415bb1e</v>
+        <v>a99bff34-c1b8-4ff2-a9ab-7b29d74471b0</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>f8b3b07e-b381-4bc5-a8ad-382ad189a9eb</v>
+        <v>ff055e7f-dbe7-43e1-8043-7c450c5350f6</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>a99bff34-c1b8-4ff2-a9ab-7b29d74471b0</v>
+        <v>5dea4df7-4077-4980-899e-5dbcd035573b</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>cd81d97b-0b7e-40e2-b4aa-16dd09663cd5</v>
+        <v>9599422f-e6a7-40d7-a5d2-9428f1c7c070</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>2274ef39-35af-4e6b-bf6c-61528af791a3</v>
+        <v>e3e1213a-6a09-4448-ab69-8475a7bd5504</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-18T07:58:34.037Z</v>
+        <v>2026-09-18T10:03:52.772Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2ee01bda-f81e-4382-acb7-233ff975f857</v>
+        <v>7d72191f-f055-4316-a76c-31b182d3804a</v>
       </c>
       <c r="B2" t="str">
-        <v>390c4952-6e15-4b47-b902-1b7a21d792de</v>
+        <v>f8a68fb8-b5ba-4d1c-b0ef-151c9123af9d</v>
       </c>
       <c r="C2" t="str">
-        <v>a99bff34-c1b8-4ff2-a9ab-7b29d74471b0</v>
+        <v>5dea4df7-4077-4980-899e-5dbcd035573b</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>ff055e7f-dbe7-43e1-8043-7c450c5350f6</v>
+        <v>17a2c309-1213-4bc9-a9e2-fa84cef05c43</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>5dea4df7-4077-4980-899e-5dbcd035573b</v>
+        <v>118dd707-f8cd-4319-b687-4c1e66352b24</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>9599422f-e6a7-40d7-a5d2-9428f1c7c070</v>
+        <v>290b2396-3bc5-43f8-8a4e-e1ed24d797ff</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>e3e1213a-6a09-4448-ab69-8475a7bd5504</v>
+        <v>0844a1b1-a170-4824-9f74-409921ea4115</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-18T10:03:52.772Z</v>
+        <v>2026-09-18T10:26:26.512Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7d72191f-f055-4316-a76c-31b182d3804a</v>
+        <v>12523607-93bd-4a49-a9e7-99b77bb97f0d</v>
       </c>
       <c r="B2" t="str">
-        <v>f8a68fb8-b5ba-4d1c-b0ef-151c9123af9d</v>
+        <v>914d95f4-c07c-433e-9441-2c579b8b6041</v>
       </c>
       <c r="C2" t="str">
-        <v>5dea4df7-4077-4980-899e-5dbcd035573b</v>
+        <v>118dd707-f8cd-4319-b687-4c1e66352b24</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>17a2c309-1213-4bc9-a9e2-fa84cef05c43</v>
+        <v>304bafe6-d5c5-4c20-913f-56f8d363d4d4</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>118dd707-f8cd-4319-b687-4c1e66352b24</v>
+        <v>53a7fde2-e33b-45ee-bb32-2ddd4ebe8b2b</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>290b2396-3bc5-43f8-8a4e-e1ed24d797ff</v>
+        <v>664eea51-4d1b-4b76-8f15-572c7477db61</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>0844a1b1-a170-4824-9f74-409921ea4115</v>
+        <v>80d30898-e27d-457d-b003-30ae43d805ce</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-18T10:26:26.512Z</v>
+        <v>2026-09-18T12:40:59.946Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12523607-93bd-4a49-a9e7-99b77bb97f0d</v>
+        <v>40467351-8cc4-4611-8ab6-2387a6570e6e</v>
       </c>
       <c r="B2" t="str">
-        <v>914d95f4-c07c-433e-9441-2c579b8b6041</v>
+        <v>531587a7-a6a5-4d29-8fb8-3475ab82f64d</v>
       </c>
       <c r="C2" t="str">
-        <v>118dd707-f8cd-4319-b687-4c1e66352b24</v>
+        <v>53a7fde2-e33b-45ee-bb32-2ddd4ebe8b2b</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>304bafe6-d5c5-4c20-913f-56f8d363d4d4</v>
+        <v>16cd1390-d395-4891-9f97-458f47d86a0c</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>53a7fde2-e33b-45ee-bb32-2ddd4ebe8b2b</v>
+        <v>41c1a0c1-d4a5-49d9-ab9a-560eede7c86e</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>664eea51-4d1b-4b76-8f15-572c7477db61</v>
+        <v>9cef01ec-b064-4d04-b1d2-0359ef499f28</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>80d30898-e27d-457d-b003-30ae43d805ce</v>
+        <v>4f77e959-a955-4d8d-9c94-327c6e018b41</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-18T12:40:59.946Z</v>
+        <v>2026-09-18T13:39:38.118Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>40467351-8cc4-4611-8ab6-2387a6570e6e</v>
+        <v>b1e519e0-e9d0-453d-a23b-18c837338dd7</v>
       </c>
       <c r="B2" t="str">
-        <v>531587a7-a6a5-4d29-8fb8-3475ab82f64d</v>
+        <v>c7a48af1-146f-4c9a-a776-50b2202a6b44</v>
       </c>
       <c r="C2" t="str">
-        <v>53a7fde2-e33b-45ee-bb32-2ddd4ebe8b2b</v>
+        <v>41c1a0c1-d4a5-49d9-ab9a-560eede7c86e</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>16cd1390-d395-4891-9f97-458f47d86a0c</v>
+        <v>264ceb82-dbfa-4219-976d-b2ea5a1c4861</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>41c1a0c1-d4a5-49d9-ab9a-560eede7c86e</v>
+        <v>9533ceba-5e0c-4f5b-8843-003253815d4f</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>9cef01ec-b064-4d04-b1d2-0359ef499f28</v>
+        <v>6e48e205-b467-462f-a2e3-2b1d3f208b57</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>4f77e959-a955-4d8d-9c94-327c6e018b41</v>
+        <v>b24db865-9bde-489d-b53e-fdbbd28ae400</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-18T13:39:38.118Z</v>
+        <v>2026-09-18T15:39:50.378Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>b1e519e0-e9d0-453d-a23b-18c837338dd7</v>
+        <v>fbba9896-c048-446d-a07f-ed258d0b61b7</v>
       </c>
       <c r="B2" t="str">
-        <v>c7a48af1-146f-4c9a-a776-50b2202a6b44</v>
+        <v>23b5d0a8-b03e-448e-96f9-2297eb1de3e4</v>
       </c>
       <c r="C2" t="str">
-        <v>41c1a0c1-d4a5-49d9-ab9a-560eede7c86e</v>
+        <v>9533ceba-5e0c-4f5b-8843-003253815d4f</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>264ceb82-dbfa-4219-976d-b2ea5a1c4861</v>
+        <v>518b0346-6994-4250-846c-938f7bbebd22</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>9533ceba-5e0c-4f5b-8843-003253815d4f</v>
+        <v>43587e88-43f4-4188-b3d3-72c16f3fdbde</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>6e48e205-b467-462f-a2e3-2b1d3f208b57</v>
+        <v>eecde874-a6a7-453b-b39c-af27c73652af</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>b24db865-9bde-489d-b53e-fdbbd28ae400</v>
+        <v>ce48b262-3b29-4b3d-a726-a78e3a2a161c</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-18T15:39:50.378Z</v>
+        <v>2026-09-18T15:52:56.081Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>fbba9896-c048-446d-a07f-ed258d0b61b7</v>
+        <v>176784b2-d6a4-4eab-92da-a68747a40195</v>
       </c>
       <c r="B2" t="str">
-        <v>23b5d0a8-b03e-448e-96f9-2297eb1de3e4</v>
+        <v>eaf8abd9-8850-4f35-a25c-edda0d702d26</v>
       </c>
       <c r="C2" t="str">
-        <v>9533ceba-5e0c-4f5b-8843-003253815d4f</v>
+        <v>43587e88-43f4-4188-b3d3-72c16f3fdbde</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>518b0346-6994-4250-846c-938f7bbebd22</v>
+        <v>6785596e-dd32-4d09-8459-6ea3b8434b79</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>43587e88-43f4-4188-b3d3-72c16f3fdbde</v>
+        <v>f028d790-a514-45b7-8a9c-5266319bcebb</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>eecde874-a6a7-453b-b39c-af27c73652af</v>
+        <v>8c38a014-2f25-439e-91fd-3e28cb63691b</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>ce48b262-3b29-4b3d-a726-a78e3a2a161c</v>
+        <v>64fdc1f7-8478-427d-b962-7971ec1d33d4</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-18T15:52:56.081Z</v>
+        <v>2026-09-18T16:37:07.442Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>176784b2-d6a4-4eab-92da-a68747a40195</v>
+        <v>5777dfda-6e10-42ad-afe6-dc6d7eac16b2</v>
       </c>
       <c r="B2" t="str">
-        <v>eaf8abd9-8850-4f35-a25c-edda0d702d26</v>
+        <v>783d5dac-7794-4418-925d-c50c5e355c00</v>
       </c>
       <c r="C2" t="str">
-        <v>43587e88-43f4-4188-b3d3-72c16f3fdbde</v>
+        <v>f028d790-a514-45b7-8a9c-5266319bcebb</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>6785596e-dd32-4d09-8459-6ea3b8434b79</v>
+        <v>663a658a-edc9-4cb8-b361-5147ecbe8292</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>f028d790-a514-45b7-8a9c-5266319bcebb</v>
+        <v>761a5383-f386-428d-a5a9-c291cee2a271</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>8c38a014-2f25-439e-91fd-3e28cb63691b</v>
+        <v>316fd80b-d5a2-4931-8dfd-4e2a780d8995</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>64fdc1f7-8478-427d-b962-7971ec1d33d4</v>
+        <v>20439a7c-a6b7-4e63-b83c-3ddef9a24f09</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-18T16:37:07.442Z</v>
+        <v>2026-09-21T09:57:39.770Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>5777dfda-6e10-42ad-afe6-dc6d7eac16b2</v>
+        <v>872c4c4a-256b-4ae5-b945-005ec58031a4</v>
       </c>
       <c r="B2" t="str">
-        <v>783d5dac-7794-4418-925d-c50c5e355c00</v>
+        <v>2dc85717-196f-4d94-b27a-37d4bead0eb1</v>
       </c>
       <c r="C2" t="str">
-        <v>f028d790-a514-45b7-8a9c-5266319bcebb</v>
+        <v>761a5383-f386-428d-a5a9-c291cee2a271</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>663a658a-edc9-4cb8-b361-5147ecbe8292</v>
+        <v>0ccea467-521e-4783-a856-713369a9f521</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>761a5383-f386-428d-a5a9-c291cee2a271</v>
+        <v>e9f656b8-5d82-4c5b-94ba-4e84b2bbcb40</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>316fd80b-d5a2-4931-8dfd-4e2a780d8995</v>
+        <v>b6797901-ccd1-4cf9-8a81-6a5e69168974</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>20439a7c-a6b7-4e63-b83c-3ddef9a24f09</v>
+        <v>86778fbc-fc54-4a0e-8aa3-f32e2985faff</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-21T09:57:39.770Z</v>
+        <v>2026-09-21T11:39:41.633Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>872c4c4a-256b-4ae5-b945-005ec58031a4</v>
+        <v>52443c7c-176c-474e-93c3-4d40a1cb407e</v>
       </c>
       <c r="B2" t="str">
-        <v>2dc85717-196f-4d94-b27a-37d4bead0eb1</v>
+        <v>22304a79-5908-4ec8-b822-9aa79620dcd2</v>
       </c>
       <c r="C2" t="str">
-        <v>761a5383-f386-428d-a5a9-c291cee2a271</v>
+        <v>e9f656b8-5d82-4c5b-94ba-4e84b2bbcb40</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
+++ b/outputs/full-aura-audit/wave2-tender-pricing-proof.xlsx
@@ -437,7 +437,7 @@
         <v>Tender ID</v>
       </c>
       <c r="B4" t="str">
-        <v>0ccea467-521e-4783-a856-713369a9f521</v>
+        <v>3e64c4cd-c192-4cb0-92e4-e64cb10917ed</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>Technical Study ID</v>
       </c>
       <c r="B10" t="str">
-        <v>e9f656b8-5d82-4c5b-94ba-4e84b2bbcb40</v>
+        <v>9436d3fe-5bdf-4ffe-9198-1bbeda61cbcd</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>BOQ ID</v>
       </c>
       <c r="B13" t="str">
-        <v>b6797901-ccd1-4cf9-8a81-6a5e69168974</v>
+        <v>b7b0a074-6b0a-4ee8-977d-c80a0057aa01</v>
       </c>
     </row>
     <row r="14">
@@ -517,7 +517,7 @@
         <v>Approved Quantity Take-Off ID</v>
       </c>
       <c r="B14" t="str">
-        <v>86778fbc-fc54-4a0e-8aa3-f32e2985faff</v>
+        <v>9bde028b-31e6-422a-a248-c28fa8fa8ec7</v>
       </c>
     </row>
     <row r="15">
@@ -533,7 +533,7 @@
         <v>Quantity projection time</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-21T11:39:41.633Z</v>
+        <v>2026-09-21T12:11:41.415Z</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>52443c7c-176c-474e-93c3-4d40a1cb407e</v>
+        <v>62a77376-ceb2-49b3-8829-c77dccf3537a</v>
       </c>
       <c r="B2" t="str">
-        <v>22304a79-5908-4ec8-b822-9aa79620dcd2</v>
+        <v>12fae59f-2a00-447b-ae91-42ba080aa265</v>
       </c>
       <c r="C2" t="str">
-        <v>e9f656b8-5d82-4c5b-94ba-4e84b2bbcb40</v>
+        <v>9436d3fe-5bdf-4ffe-9198-1bbeda61cbcd</v>
       </c>
       <c r="D2">
         <v>1</v>
